--- a/data/Benchmarks/Election Returns/Governor_Returns_2006_2022.xlsx
+++ b/data/Benchmarks/Election Returns/Governor_Returns_2006_2022.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jdpruett/Desktop/CES Accuracy Analysis/data/Election Validation/Final Sets - Clean Fixed/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jdpruett/Desktop/CES Accuracy Analysis/data/Benchmarks/Election Returns/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C08393DD-A83E-2D4A-9C1F-15795EAAB283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF387911-8322-8544-A9C2-F24C38831327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2380" yWindow="1020" windowWidth="24220" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8780" uniqueCount="1020">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8783" uniqueCount="1020">
   <si>
     <t>year</t>
   </si>
@@ -46046,6 +46046,9 @@
       <c r="P829">
         <v>2</v>
       </c>
+      <c r="Q829" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="830" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A830">
@@ -46097,6 +46100,9 @@
       <c r="P830">
         <v>1</v>
       </c>
+      <c r="Q830" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="831" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A831">
@@ -46143,6 +46149,9 @@
       </c>
       <c r="O831" t="s">
         <v>31</v>
+      </c>
+      <c r="Q831" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="832" spans="1:17" x14ac:dyDescent="0.2">
